--- a/outputs/48527.xlsx
+++ b/outputs/48527.xlsx
@@ -140,11 +140,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -368,8 +368,8 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="str">
-        <f aca="false">_xlfn.UNIQUE(_xlfn._xlws.FILTER(C2:C5,A2:A5=B2:B5))</f>
-        <v>Orange</v>
+        <f aca="false">IF(A2=B2,C2,"")</f>
+        <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -382,7 +382,10 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="str">
+        <f aca="false">IF(A3=B3,C3,"")</f>
+        <v>Orange</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -394,7 +397,10 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="str">
+        <f aca="false">IF(A4=B4,C4,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -406,7 +412,10 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="str">
+        <f aca="false">IF(A5=B5,C5,"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/48527.xlsx
+++ b/outputs/48527.xlsx
@@ -368,8 +368,8 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="str">
-        <f aca="false">IF(A2=B2,C2,"")</f>
-        <v/>
+        <f aca="false">IFERROR(INDEX($C$2:$C$5,MATCH(0,COUNTIF($D$1:D1,$C$2:$C$5)+($A$2:$A$5&lt;&gt;$B$2:$B$5),0)),"")</f>
+        <v>Orange</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -383,7 +383,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="str">
-        <f aca="false">IF(A3=B3,C3,"")</f>
+        <f aca="false">IFERROR(INDEX($C$2:$C$5,MATCH(0,COUNTIF($D$1:D1,$C$2:$C$5)+($A$2:$A$5&lt;&gt;$B$2:$B$5),0)),"")</f>
         <v>Orange</v>
       </c>
     </row>
@@ -398,8 +398,8 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="str">
-        <f aca="false">IF(A4=B4,C4,"")</f>
-        <v/>
+        <f aca="false">IFERROR(INDEX($C$2:$C$5,MATCH(0,COUNTIF($D$1:D1,$C$2:$C$5)+($A$2:$A$5&lt;&gt;$B$2:$B$5),0)),"")</f>
+        <v>Orange</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -413,8 +413,8 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="str">
-        <f aca="false">IF(A5=B5,C5,"")</f>
-        <v/>
+        <f aca="false">IFERROR(INDEX($C$2:$C$5,MATCH(0,COUNTIF($D$1:D1,$C$2:$C$5)+($A$2:$A$5&lt;&gt;$B$2:$B$5),0)),"")</f>
+        <v>Orange</v>
       </c>
     </row>
   </sheetData>
